--- a/data/trans_orig/P19C04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C04-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28862</t>
+          <t>28719</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51062</t>
+          <t>51685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40428</t>
+          <t>39946</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52899</t>
+          <t>53958</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86138</t>
+          <t>84073</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>308339</t>
+          <t>307716</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>330539</t>
+          <t>330682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335824</t>
+          <t>336306</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>355638</t>
+          <t>356348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>649515</t>
+          <t>651580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>682754</t>
+          <t>681695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64284</t>
+          <t>64673</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101705</t>
+          <t>98302</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46111</t>
+          <t>45427</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76621</t>
+          <t>75811</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117518</t>
+          <t>120018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163470</t>
+          <t>163870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>474076</t>
+          <t>477479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511497</t>
+          <t>511108</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471087</t>
+          <t>471897</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>501597</t>
+          <t>502281</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>960019</t>
+          <t>959619</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1005971</t>
+          <t>1003471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78091</t>
+          <t>76446</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>114259</t>
+          <t>110979</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62085</t>
+          <t>62113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96512</t>
+          <t>94221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146670</t>
+          <t>147600</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197390</t>
+          <t>196525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>388674</t>
+          <t>391954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>424842</t>
+          <t>426487</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>507053</t>
+          <t>509344</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541480</t>
+          <t>541452</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>909107</t>
+          <t>909972</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>959827</t>
+          <t>958897</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93898</t>
+          <t>92232</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131268</t>
+          <t>129490</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72559</t>
+          <t>72040</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105409</t>
+          <t>104362</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>174731</t>
+          <t>173584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225347</t>
+          <t>224742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>273480</t>
+          <t>275258</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310850</t>
+          <t>312516</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>334823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366626</t>
+          <t>367145</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>618586</t>
+          <t>619191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>669202</t>
+          <t>670349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58414</t>
+          <t>57044</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87618</t>
+          <t>85078</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50763</t>
+          <t>51523</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79545</t>
+          <t>80273</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115276</t>
+          <t>116196</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>156165</t>
+          <t>157698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>184731</t>
+          <t>187271</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>213935</t>
+          <t>215305</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>239537</t>
+          <t>238809</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>268319</t>
+          <t>267559</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>435266</t>
+          <t>433733</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>476155</t>
+          <t>475235</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,35%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50836</t>
+          <t>49767</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77115</t>
+          <t>76237</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38331</t>
+          <t>37922</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61166</t>
+          <t>61711</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92247</t>
+          <t>93900</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127603</t>
+          <t>129805</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>135650</t>
+          <t>136528</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161929</t>
+          <t>162998</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>185772</t>
+          <t>185227</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208607</t>
+          <t>209016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>332100</t>
+          <t>329898</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>367456</t>
+          <t>365803</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>41314</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23121</t>
+          <t>24049</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47109</t>
+          <t>46369</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52038</t>
+          <t>51496</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83293</t>
+          <t>82722</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>84722</t>
+          <t>85450</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104692</t>
+          <t>104366</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>161099</t>
+          <t>161839</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>185087</t>
+          <t>184159</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>251679</t>
+          <t>252250</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>282934</t>
+          <t>283476</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>450878</t>
+          <t>449175</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>531386</t>
+          <t>530224</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>364094</t>
+          <t>368865</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>437561</t>
+          <t>439813</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>834415</t>
+          <t>838333</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>948895</t>
+          <t>946159</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1923356</t>
+          <t>1924518</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2003864</t>
+          <t>2005567</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2303376</t>
+          <t>2301124</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2376843</t>
+          <t>2372072</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4246784</t>
+          <t>4249520</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4361264</t>
+          <t>4357346</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40249</t>
+          <t>39087</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67154</t>
+          <t>66703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36901</t>
+          <t>36013</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62545</t>
+          <t>61587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82265</t>
+          <t>82852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120142</t>
+          <t>122629</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>312022</t>
+          <t>312473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>338927</t>
+          <t>340089</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308446</t>
+          <t>309404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>334090</t>
+          <t>334978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>630024</t>
+          <t>627537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>667901</t>
+          <t>667314</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,96%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92010</t>
+          <t>92412</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131165</t>
+          <t>132298</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52527</t>
+          <t>52324</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82476</t>
+          <t>83578</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>150233</t>
+          <t>152158</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>199724</t>
+          <t>201459</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>466102</t>
+          <t>464969</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505257</t>
+          <t>504855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475269</t>
+          <t>474167</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505218</t>
+          <t>505421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>955288</t>
+          <t>953553</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1004779</t>
+          <t>1002854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>114133</t>
+          <t>115032</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156451</t>
+          <t>155466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78755</t>
+          <t>78097</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115824</t>
+          <t>116482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200991</t>
+          <t>200876</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>257921</t>
+          <t>255822</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>430200</t>
+          <t>431185</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>472518</t>
+          <t>471619</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>543630</t>
+          <t>542972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>580699</t>
+          <t>581357</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>988183</t>
+          <t>990282</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1045113</t>
+          <t>1045228</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,88%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112517</t>
+          <t>114226</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>156790</t>
+          <t>159338</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82094</t>
+          <t>82689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121696</t>
+          <t>124909</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>207853</t>
+          <t>209005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>266434</t>
+          <t>264663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>386049</t>
+          <t>383501</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>430322</t>
+          <t>428613</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>441655</t>
+          <t>438442</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>481257</t>
+          <t>480662</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>839756</t>
+          <t>841527</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>898337</t>
+          <t>897185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98047</t>
+          <t>96320</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134135</t>
+          <t>133566</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70248</t>
+          <t>70138</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104644</t>
+          <t>104765</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178864</t>
+          <t>176231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>229496</t>
+          <t>226087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>227175</t>
+          <t>227744</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>263263</t>
+          <t>264990</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>285043</t>
+          <t>284922</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319439</t>
+          <t>319549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>521501</t>
+          <t>524910</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>572133</t>
+          <t>574766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,53%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86224</t>
+          <t>85923</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>120081</t>
+          <t>119197</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57639</t>
+          <t>57451</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87002</t>
+          <t>87786</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>150185</t>
+          <t>150844</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>195227</t>
+          <t>197296</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>142409</t>
+          <t>143293</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>176266</t>
+          <t>176567</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>213587</t>
+          <t>212803</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>242950</t>
+          <t>243138</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>367852</t>
+          <t>365783</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>412894</t>
+          <t>412235</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,21%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58888</t>
+          <t>58616</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>88820</t>
+          <t>89406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67368</t>
+          <t>66518</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98546</t>
+          <t>98517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133888</t>
+          <t>133474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>179479</t>
+          <t>177661</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96106</t>
+          <t>95520</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>126038</t>
+          <t>126310</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>204859</t>
+          <t>204888</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>236037</t>
+          <t>236887</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>308852</t>
+          <t>310670</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>354443</t>
+          <t>354857</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,67%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>672392</t>
+          <t>676315</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>772075</t>
+          <t>774731</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>509695</t>
+          <t>507321</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>593783</t>
+          <t>592332</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1210693</t>
+          <t>1204086</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1340636</t>
+          <t>1338789</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2142584</t>
+          <t>2139928</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2242267</t>
+          <t>2238344</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2551438</t>
+          <t>2552889</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2635526</t>
+          <t>2637900</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4719243</t>
+          <t>4721090</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4849186</t>
+          <t>4855793</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2016 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22405</t>
+          <t>22267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44866</t>
+          <t>44944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21360</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41068</t>
+          <t>41742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48351</t>
+          <t>48459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77573</t>
+          <t>79287</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307974</t>
+          <t>307896</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>330435</t>
+          <t>330573</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>310862</t>
+          <t>310188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>330570</t>
+          <t>331056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>627197</t>
+          <t>625483</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>656419</t>
+          <t>656311</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,12%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56630</t>
+          <t>55928</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87510</t>
+          <t>89229</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46005</t>
+          <t>46191</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74431</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110400</t>
+          <t>111026</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151557</t>
+          <t>152855</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>405568</t>
+          <t>403849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>436448</t>
+          <t>437150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>422289</t>
+          <t>421315</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>450715</t>
+          <t>450529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>838240</t>
+          <t>836942</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>879397</t>
+          <t>878771</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63646</t>
+          <t>63106</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96083</t>
+          <t>95878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45796</t>
+          <t>47038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75516</t>
+          <t>75160</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117121</t>
+          <t>116999</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163671</t>
+          <t>162790</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>461777</t>
+          <t>461982</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>494214</t>
+          <t>494754</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>497564</t>
+          <t>497920</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>527284</t>
+          <t>526042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>967269</t>
+          <t>968150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1013819</t>
+          <t>1013941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75203</t>
+          <t>75603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111253</t>
+          <t>112460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51087</t>
+          <t>50527</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82783</t>
+          <t>81457</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131310</t>
+          <t>133668</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181833</t>
+          <t>183172</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>401119</t>
+          <t>399912</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>437169</t>
+          <t>436769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>462101</t>
+          <t>463427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>493797</t>
+          <t>494357</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>875423</t>
+          <t>874084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>925946</t>
+          <t>923588</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81627</t>
+          <t>80166</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>116646</t>
+          <t>114554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39276</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68239</t>
+          <t>66259</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128142</t>
+          <t>126651</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174923</t>
+          <t>176143</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>254356</t>
+          <t>256448</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>289375</t>
+          <t>290836</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326540</t>
+          <t>328520</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>355503</t>
+          <t>356341</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>590857</t>
+          <t>589637</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>637638</t>
+          <t>639129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49253</t>
+          <t>49032</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75545</t>
+          <t>76322</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36494</t>
+          <t>36674</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61725</t>
+          <t>62357</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93410</t>
+          <t>91936</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130128</t>
+          <t>130684</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154580</t>
+          <t>153803</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>180872</t>
+          <t>181093</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>215223</t>
+          <t>214591</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>240454</t>
+          <t>240274</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>376946</t>
+          <t>376390</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>413664</t>
+          <t>415138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,87%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32277</t>
+          <t>32027</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51354</t>
+          <t>52441</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44367</t>
+          <t>44216</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74623</t>
+          <t>74246</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82024</t>
+          <t>81240</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116494</t>
+          <t>116971</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95703</t>
+          <t>94616</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>114780</t>
+          <t>115030</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>153256</t>
+          <t>153633</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>183512</t>
+          <t>183663</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>258442</t>
+          <t>257965</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>292912</t>
+          <t>293696</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>436630</t>
+          <t>437264</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>518235</t>
+          <t>516550</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,82 +9107,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>16,41%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>373344</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>333507</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>410704</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>849072</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>796671</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>906223</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>15,35%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>16,39%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>19,45%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>373344</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>335473</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>413296</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>11,7%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>14,42%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>849072</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>794359</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>903583</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>14,36%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2146098</t>
+          <t>2147783</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2227703</t>
+          <t>2227069</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,82 +9220,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>83,59%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2381</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2492877</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2455517</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2532714</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>86,97%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>88,36%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>4457</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>4681482</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>4624331</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>4733883</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>84,65%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>83,61%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2381</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>2492877</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>2452925</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2530748</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>86,97%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>85,58%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>88,3%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>4457</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>4681482</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>4626971</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4736195</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>84,65%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>83,66%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,6%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2023 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52784</t>
+          <t>51643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22417</t>
+          <t>20953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>25075</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66205</t>
+          <t>67080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>330663</t>
+          <t>331804</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>369016</t>
+          <t>369841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281124</t>
+          <t>282588</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297900</t>
+          <t>298076</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>620783</t>
+          <t>619908</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>663191</t>
+          <t>661913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30201</t>
+          <t>30456</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61410</t>
+          <t>63772</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22452</t>
+          <t>20951</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53323</t>
+          <t>51781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60118</t>
+          <t>58489</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105872</t>
+          <t>105158</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340941</t>
+          <t>338579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372150</t>
+          <t>371895</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>446369</t>
+          <t>447911</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>477240</t>
+          <t>478741</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>796170</t>
+          <t>796884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>841924</t>
+          <t>843553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45830</t>
+          <t>47325</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76923</t>
+          <t>78175</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>35582</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57235</t>
+          <t>57916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89791</t>
+          <t>89466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125461</t>
+          <t>125059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446022</t>
+          <t>444770</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477115</t>
+          <t>475620</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>474646</t>
+          <t>473965</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>495635</t>
+          <t>496299</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>929366</t>
+          <t>929768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>965036</t>
+          <t>965361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37499</t>
+          <t>39234</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131110</t>
+          <t>131508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51834</t>
+          <t>51382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77166</t>
+          <t>76559</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89972</t>
+          <t>87861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192938</t>
+          <t>192189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>731818</t>
+          <t>731420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>825429</t>
+          <t>823694</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>623426</t>
+          <t>624033</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648758</t>
+          <t>649210</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1370581</t>
+          <t>1371330</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1473547</t>
+          <t>1475658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93572</t>
+          <t>90937</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126913</t>
+          <t>124655</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63465</t>
+          <t>62610</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86497</t>
+          <t>85849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>161179</t>
+          <t>164207</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>204450</t>
+          <t>204371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>419666</t>
+          <t>421924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>453007</t>
+          <t>455642</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>448029</t>
+          <t>448677</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>471061</t>
+          <t>471916</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>876655</t>
+          <t>876734</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>919926</t>
+          <t>916898</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,81%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>70386</t>
+          <t>71535</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96510</t>
+          <t>96937</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22524</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99062</t>
+          <t>100474</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77649</t>
+          <t>74959</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>195240</t>
+          <t>193941</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262843</t>
+          <t>262416</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288967</t>
+          <t>287818</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>500847</t>
+          <t>499435</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>577385</t>
+          <t>575876</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>764022</t>
+          <t>765321</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>881613</t>
+          <t>884303</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57956</t>
+          <t>59772</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80251</t>
+          <t>80584</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68528</t>
+          <t>68164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90288</t>
+          <t>90714</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>135330</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165009</t>
+          <t>167002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195270</t>
+          <t>194937</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>217565</t>
+          <t>215749</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>318399</t>
+          <t>317973</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>340159</t>
+          <t>340523</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>519199</t>
+          <t>517206</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>549147</t>
+          <t>548878</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>374856</t>
+          <t>376258</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>544619</t>
+          <t>540180</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>308764</t>
+          <t>305337</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>417583</t>
+          <t>415367</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>745530</t>
+          <t>757706</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>940970</t>
+          <t>944760</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2808506</t>
+          <t>2812945</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2978269</t>
+          <t>2976867</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3161244</t>
+          <t>3163460</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3270063</t>
+          <t>3273490</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5990982</t>
+          <t>5987192</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6186422</t>
+          <t>6174246</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C04-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28719</t>
+          <t>27859</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51685</t>
+          <t>51373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39946</t>
+          <t>40339</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53958</t>
+          <t>52773</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84073</t>
+          <t>83756</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307716</t>
+          <t>308028</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>330682</t>
+          <t>331542</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>336306</t>
+          <t>335913</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>356348</t>
+          <t>356228</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>651580</t>
+          <t>651897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>681695</t>
+          <t>682880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64673</t>
+          <t>64801</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98302</t>
+          <t>99245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45427</t>
+          <t>46274</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75811</t>
+          <t>75497</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120018</t>
+          <t>117729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163870</t>
+          <t>162685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477479</t>
+          <t>476536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>511108</t>
+          <t>510980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471897</t>
+          <t>472211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502281</t>
+          <t>501434</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>959619</t>
+          <t>960804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1003471</t>
+          <t>1005760</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76446</t>
+          <t>75738</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110979</t>
+          <t>110891</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62113</t>
+          <t>61398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94221</t>
+          <t>94064</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147600</t>
+          <t>146027</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196525</t>
+          <t>194879</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>391954</t>
+          <t>392042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426487</t>
+          <t>427195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>509344</t>
+          <t>509501</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541452</t>
+          <t>542167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>909972</t>
+          <t>911618</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>958897</t>
+          <t>960470</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92232</t>
+          <t>91410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129490</t>
+          <t>130076</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72040</t>
+          <t>71912</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104362</t>
+          <t>105580</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173584</t>
+          <t>174467</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>224742</t>
+          <t>225083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275258</t>
+          <t>274672</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312516</t>
+          <t>313338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>334823</t>
+          <t>333605</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367145</t>
+          <t>367273</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>619191</t>
+          <t>618850</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>670349</t>
+          <t>669466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57044</t>
+          <t>57553</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85078</t>
+          <t>86978</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51523</t>
+          <t>50635</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80273</t>
+          <t>78866</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116196</t>
+          <t>116573</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157698</t>
+          <t>157347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>187271</t>
+          <t>185371</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>215305</t>
+          <t>214796</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>238809</t>
+          <t>240216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>267559</t>
+          <t>268447</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>433733</t>
+          <t>434084</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>475235</t>
+          <t>474858</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49767</t>
+          <t>50798</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76237</t>
+          <t>76512</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37922</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61711</t>
+          <t>61060</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93900</t>
+          <t>97114</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>129805</t>
+          <t>131527</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136528</t>
+          <t>136253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162998</t>
+          <t>161967</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>185227</t>
+          <t>185878</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209016</t>
+          <t>208615</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>329898</t>
+          <t>328176</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>365803</t>
+          <t>362589</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>78,87%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>21583</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41314</t>
+          <t>41292</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24049</t>
+          <t>24229</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46369</t>
+          <t>47109</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51496</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82722</t>
+          <t>81648</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85450</t>
+          <t>85472</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>104366</t>
+          <t>105181</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>161839</t>
+          <t>161099</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>184159</t>
+          <t>183979</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>252250</t>
+          <t>253324</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283476</t>
+          <t>283469</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>449175</t>
+          <t>452315</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>530224</t>
+          <t>532460</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>368865</t>
+          <t>368079</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>439813</t>
+          <t>443924</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>838333</t>
+          <t>838459</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>946159</t>
+          <t>950149</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1924518</t>
+          <t>1922282</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2005567</t>
+          <t>2002427</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2301124</t>
+          <t>2297013</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2372072</t>
+          <t>2372858</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4249520</t>
+          <t>4245530</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4357346</t>
+          <t>4357220</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39087</t>
+          <t>39310</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66703</t>
+          <t>67262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36013</t>
+          <t>36635</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61587</t>
+          <t>62175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82852</t>
+          <t>84586</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122629</t>
+          <t>122681</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>312473</t>
+          <t>311914</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>340089</t>
+          <t>339866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309404</t>
+          <t>308816</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>334978</t>
+          <t>334356</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>627537</t>
+          <t>627485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>667314</t>
+          <t>665580</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92412</t>
+          <t>93802</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>132298</t>
+          <t>131131</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52324</t>
+          <t>52554</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83578</t>
+          <t>82763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152158</t>
+          <t>151949</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>201459</t>
+          <t>201899</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>464969</t>
+          <t>466136</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504855</t>
+          <t>503465</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>474167</t>
+          <t>474982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505421</t>
+          <t>505191</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953553</t>
+          <t>953113</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1002854</t>
+          <t>1003063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115032</t>
+          <t>114838</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155466</t>
+          <t>155167</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78097</t>
+          <t>77564</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116482</t>
+          <t>113145</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200876</t>
+          <t>203301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255822</t>
+          <t>258538</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>431185</t>
+          <t>431484</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>471619</t>
+          <t>471813</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>542972</t>
+          <t>546309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>581357</t>
+          <t>581890</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>990282</t>
+          <t>987566</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1045228</t>
+          <t>1042803</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114226</t>
+          <t>112694</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159338</t>
+          <t>155237</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82689</t>
+          <t>84454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124909</t>
+          <t>124130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>209005</t>
+          <t>209137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>264663</t>
+          <t>264824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>383501</t>
+          <t>387602</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>428613</t>
+          <t>430145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>438442</t>
+          <t>439221</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>480662</t>
+          <t>478897</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>841527</t>
+          <t>841366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>897185</t>
+          <t>897053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96320</t>
+          <t>98172</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133566</t>
+          <t>136187</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70138</t>
+          <t>71330</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104765</t>
+          <t>105541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>176231</t>
+          <t>179279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226087</t>
+          <t>227392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>227744</t>
+          <t>225123</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>264990</t>
+          <t>263138</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>284922</t>
+          <t>284146</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>319549</t>
+          <t>318357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>524910</t>
+          <t>523605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>574766</t>
+          <t>571718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,13%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85923</t>
+          <t>85783</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119197</t>
+          <t>120343</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57451</t>
+          <t>57618</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>87786</t>
+          <t>86350</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>150844</t>
+          <t>148507</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197296</t>
+          <t>196420</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>143293</t>
+          <t>142147</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>176567</t>
+          <t>176707</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>212803</t>
+          <t>214239</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243138</t>
+          <t>242971</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>365783</t>
+          <t>366659</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>412235</t>
+          <t>414572</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58616</t>
+          <t>60664</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>89406</t>
+          <t>87923</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66518</t>
+          <t>66574</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98517</t>
+          <t>97048</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133474</t>
+          <t>135852</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177661</t>
+          <t>176175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95520</t>
+          <t>97003</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>126310</t>
+          <t>124262</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>204888</t>
+          <t>206357</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>236887</t>
+          <t>236831</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>310670</t>
+          <t>312156</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>354857</t>
+          <t>352479</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,18%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>676315</t>
+          <t>669120</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>774731</t>
+          <t>766749</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>507321</t>
+          <t>512065</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>592332</t>
+          <t>603803</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1204086</t>
+          <t>1206019</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1338789</t>
+          <t>1337771</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2139928</t>
+          <t>2147910</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2238344</t>
+          <t>2245539</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2552889</t>
+          <t>2541418</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2637900</t>
+          <t>2633156</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4721090</t>
+          <t>4722108</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4855793</t>
+          <t>4853860</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,1%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22267</t>
+          <t>22928</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44944</t>
+          <t>45473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>20457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>42118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48459</t>
+          <t>47593</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79287</t>
+          <t>79017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>307896</t>
+          <t>307367</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>330573</t>
+          <t>329912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>310188</t>
+          <t>309812</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>331056</t>
+          <t>331473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>625483</t>
+          <t>625753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>656311</t>
+          <t>657177</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55928</t>
+          <t>55556</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89229</t>
+          <t>87168</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46191</t>
+          <t>46783</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75405</t>
+          <t>73925</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111026</t>
+          <t>110397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152855</t>
+          <t>152858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403849</t>
+          <t>405910</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>437150</t>
+          <t>437522</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>421315</t>
+          <t>422795</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>450529</t>
+          <t>449937</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>836942</t>
+          <t>836939</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>878771</t>
+          <t>879400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63106</t>
+          <t>63496</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95878</t>
+          <t>97411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47038</t>
+          <t>47430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75160</t>
+          <t>75892</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116999</t>
+          <t>119327</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162790</t>
+          <t>162768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>461982</t>
+          <t>460449</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>494754</t>
+          <t>494364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>497920</t>
+          <t>497188</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>526042</t>
+          <t>525650</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>968150</t>
+          <t>968172</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1013941</t>
+          <t>1011613</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75603</t>
+          <t>75590</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112460</t>
+          <t>112180</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50527</t>
+          <t>50102</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81457</t>
+          <t>81234</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133668</t>
+          <t>134188</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183172</t>
+          <t>181660</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>399912</t>
+          <t>400192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>436769</t>
+          <t>436782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>463427</t>
+          <t>463650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>494357</t>
+          <t>494782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>874084</t>
+          <t>875596</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>923588</t>
+          <t>923068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80166</t>
+          <t>82493</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114554</t>
+          <t>117834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>39195</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>68034</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126651</t>
+          <t>128282</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>176143</t>
+          <t>174311</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>256448</t>
+          <t>253168</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>290836</t>
+          <t>288509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>328520</t>
+          <t>326745</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>356341</t>
+          <t>355584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>589637</t>
+          <t>591469</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>639129</t>
+          <t>637498</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49032</t>
+          <t>49462</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76322</t>
+          <t>75869</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36674</t>
+          <t>37340</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62357</t>
+          <t>63634</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91936</t>
+          <t>92075</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130684</t>
+          <t>129908</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153803</t>
+          <t>154256</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181093</t>
+          <t>180663</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>214591</t>
+          <t>213314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>240274</t>
+          <t>239608</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>376390</t>
+          <t>377166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>415138</t>
+          <t>414999</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32027</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52441</t>
+          <t>51676</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44216</t>
+          <t>43217</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74246</t>
+          <t>74341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81240</t>
+          <t>79277</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116971</t>
+          <t>118589</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>94616</t>
+          <t>95381</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115030</t>
+          <t>115284</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>153633</t>
+          <t>153538</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>183663</t>
+          <t>184662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>257965</t>
+          <t>256347</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>293696</t>
+          <t>295659</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>437264</t>
+          <t>439636</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>516550</t>
+          <t>519767</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>333507</t>
+          <t>337268</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>410704</t>
+          <t>413031</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>796671</t>
+          <t>790208</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>906223</t>
+          <t>899820</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2147783</t>
+          <t>2144566</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2227069</t>
+          <t>2224697</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2455517</t>
+          <t>2453190</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2532714</t>
+          <t>2528953</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4624331</t>
+          <t>4630734</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4733883</t>
+          <t>4740346</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,71%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>30181</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>15806</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51643</t>
+          <t>53728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,67 +9700,67 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20953</t>
+          <t>26780</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>45029</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>28172</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>66965</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>3,9%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>40349</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>25075</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>67080</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>354948</t>
+          <t>348673</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>331804</t>
+          <t>325126</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>369841</t>
+          <t>363048</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,67 +9813,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>291691</t>
+          <t>328392</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282588</t>
+          <t>316460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>298076</t>
+          <t>335798</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
+          <t>95,67%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>92,2%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>677065</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>655129</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>693922</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>93,76%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>90,73%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>96,1%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>646639</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>619908</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>661913</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>94,13%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>90,24%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44742</t>
+          <t>52624</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30456</t>
+          <t>36358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63772</t>
+          <t>71245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37274</t>
+          <t>43736</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>32356</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51781</t>
+          <t>57936</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>82016</t>
+          <t>96360</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58489</t>
+          <t>77093</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>105158</t>
+          <t>121758</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>357609</t>
+          <t>393269</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>338579</t>
+          <t>374648</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371895</t>
+          <t>409535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>462418</t>
+          <t>438873</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447911</t>
+          <t>424673</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>478741</t>
+          <t>450253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>820026</t>
+          <t>832142</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>796884</t>
+          <t>806744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>843553</t>
+          <t>851409</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60512</t>
+          <t>82242</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47325</t>
+          <t>65923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78175</t>
+          <t>102584</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46223</t>
+          <t>54728</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35582</t>
+          <t>43936</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57916</t>
+          <t>67151</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>106735</t>
+          <t>136970</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89466</t>
+          <t>115214</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125059</t>
+          <t>159099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,18%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>462433</t>
+          <t>517683</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>444770</t>
+          <t>497341</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>475620</t>
+          <t>534002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>485658</t>
+          <t>552554</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>473965</t>
+          <t>540131</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>496299</t>
+          <t>563346</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>948092</t>
+          <t>1070236</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>929768</t>
+          <t>1048107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>965361</t>
+          <t>1091992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>522945</t>
+          <t>599925</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>522945</t>
+          <t>599925</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>522945</t>
+          <t>599925</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1054827</t>
+          <t>1207206</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1054827</t>
+          <t>1207206</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1054827</t>
+          <t>1207206</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>89096</t>
+          <t>103276</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39234</t>
+          <t>84844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131508</t>
+          <t>121010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64312</t>
+          <t>69518</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51382</t>
+          <t>57554</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76559</t>
+          <t>82537</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>153408</t>
+          <t>172794</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87861</t>
+          <t>151213</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192189</t>
+          <t>199083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>773832</t>
+          <t>575023</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>731420</t>
+          <t>557289</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>823694</t>
+          <t>593455</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>636280</t>
+          <t>652239</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>624033</t>
+          <t>639220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>649210</t>
+          <t>664203</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1410111</t>
+          <t>1227262</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1371330</t>
+          <t>1200973</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1475658</t>
+          <t>1248843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>108312</t>
+          <t>122048</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>90937</t>
+          <t>104668</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>124655</t>
+          <t>140417</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>74245</t>
+          <t>82314</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62610</t>
+          <t>70092</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>85849</t>
+          <t>95478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>182557</t>
+          <t>204362</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164207</t>
+          <t>182781</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>204371</t>
+          <t>226370</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>438267</t>
+          <t>471307</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>421924</t>
+          <t>452938</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>455642</t>
+          <t>488687</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>460281</t>
+          <t>513535</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>448677</t>
+          <t>500371</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>471916</t>
+          <t>525757</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>898548</t>
+          <t>984842</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>876734</t>
+          <t>962834</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>916898</t>
+          <t>1006423</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>83938</t>
+          <t>90799</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>71535</t>
+          <t>77600</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96937</t>
+          <t>106767</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>63249</t>
+          <t>67703</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24033</t>
+          <t>57016</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100474</t>
+          <t>78740</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>147187</t>
+          <t>158502</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74959</t>
+          <t>141313</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>193941</t>
+          <t>176672</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>275415</t>
+          <t>306945</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262416</t>
+          <t>290977</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287818</t>
+          <t>320144</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>536660</t>
+          <t>361222</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>499435</t>
+          <t>350185</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>575876</t>
+          <t>371909</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>812075</t>
+          <t>668167</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>765321</t>
+          <t>649997</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>884303</t>
+          <t>685356</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,69 +11723,69 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>69878</t>
+          <t>74747</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59772</t>
+          <t>63343</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80584</t>
+          <t>87836</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>20,95%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>29,05%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>84268</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>73559</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>96680</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>18,9%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
           <t>21,69%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>79249</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>68164</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>90714</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>19,39%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>16,68%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>304</t>
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>149127</t>
+          <t>159015</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135330</t>
+          <t>142281</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>167002</t>
+          <t>175619</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -11836,67 +11836,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>205643</t>
+          <t>227662</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>194937</t>
+          <t>214573</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>215749</t>
+          <t>239066</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>79,05%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>361518</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>349106</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>372227</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>81,1%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>78,31%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>329438</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>317973</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>340523</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>80,61%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>77,8%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>535081</t>
+          <t>589181</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>517206</t>
+          <t>572577</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>548878</t>
+          <t>605915</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>484977</t>
+          <t>555917</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>376258</t>
+          <t>503648</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>540180</t>
+          <t>599034</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>376402</t>
+          <t>417116</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>305337</t>
+          <t>388067</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>415367</t>
+          <t>448988</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>861379</t>
+          <t>973032</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>757706</t>
+          <t>916155</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>944760</t>
+          <t>1027041</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2868148</t>
+          <t>2840562</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2812945</t>
+          <t>2797445</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2976867</t>
+          <t>2892831</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3202425</t>
+          <t>3208332</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3163460</t>
+          <t>3176460</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3273490</t>
+          <t>3237381</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6070573</t>
+          <t>6048894</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5987192</t>
+          <t>5994885</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6174246</t>
+          <t>6105771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6931952</t>
+          <t>7021926</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6931952</t>
+          <t>7021926</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6931952</t>
+          <t>7021926</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
